--- a/frontend/kskcolle/public/data/erelijsten/Ranking.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/Ranking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/Website KSK Colle/_/erelijsten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/KSKColle/frontend/kskcolle/public/data/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{377764A5-6968-4EE0-B642-9E5A90FE47FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E3C44C-07B9-43BF-B670-3F46037D701F}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{377764A5-6968-4EE0-B642-9E5A90FE47FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C34831CB-050C-436D-BAAC-D33CBC0F10D4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="0" windowWidth="16065" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking Clubkampioenschap" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="119">
   <si>
     <t>Eerste Klasse - Clubkampioenen</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>Pieter-Jan Orban</t>
+  </si>
+  <si>
+    <t>Jasper Orban</t>
   </si>
 </sst>
 </file>
@@ -618,10 +621,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -921,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="5" customWidth="1"/>
@@ -1492,7 +1491,7 @@
         <v>47</v>
       </c>
       <c r="D10" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="15">
         <v>9</v>
@@ -1700,17 +1699,17 @@
         <v>1</v>
       </c>
       <c r="L13" s="17"/>
-      <c r="M13" s="21" t="s">
-        <v>34</v>
+      <c r="M13" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="N13" s="14">
         <v>1</v>
       </c>
       <c r="O13" s="15">
+        <v>1</v>
+      </c>
+      <c r="P13" s="16">
         <v>3</v>
-      </c>
-      <c r="P13" s="16">
-        <v>1</v>
       </c>
       <c r="Q13" s="19"/>
       <c r="R13" s="21" t="s">
@@ -1763,16 +1762,16 @@
       </c>
       <c r="L14" s="17"/>
       <c r="M14" s="21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N14" s="14">
         <v>1</v>
       </c>
       <c r="O14" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" s="16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="19"/>
       <c r="R14" s="21" t="s">
@@ -1825,16 +1824,16 @@
       </c>
       <c r="L15" s="17"/>
       <c r="M15" s="21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N15" s="14">
         <v>1</v>
       </c>
       <c r="O15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q15" s="19"/>
       <c r="R15" s="21" t="s">
@@ -1887,7 +1886,7 @@
       </c>
       <c r="L16" s="17"/>
       <c r="M16" s="21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N16" s="14">
         <v>1</v>
@@ -1896,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="19"/>
       <c r="R16" s="21" t="s">
@@ -1949,7 +1948,7 @@
       </c>
       <c r="L17" s="17"/>
       <c r="M17" s="21" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N17" s="14">
         <v>1</v>
@@ -2011,7 +2010,7 @@
       </c>
       <c r="L18" s="17"/>
       <c r="M18" s="21" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N18" s="14">
         <v>1</v>
@@ -2073,7 +2072,7 @@
       </c>
       <c r="L19" s="17"/>
       <c r="M19" s="21" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="N19" s="14">
         <v>1</v>
@@ -2082,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="19"/>
       <c r="R19" s="21" t="s">
@@ -2135,16 +2134,16 @@
       </c>
       <c r="L20" s="17"/>
       <c r="M20" s="21" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="N20" s="14">
         <v>1</v>
       </c>
       <c r="O20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="19"/>
       <c r="R20" s="21" t="s">
@@ -2197,7 +2196,7 @@
       </c>
       <c r="L21" s="17"/>
       <c r="M21" s="21" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N21" s="14">
         <v>1</v>
@@ -2259,7 +2258,7 @@
       </c>
       <c r="L22" s="17"/>
       <c r="M22" s="21" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="N22" s="14">
         <v>1</v>
@@ -2321,7 +2320,7 @@
       </c>
       <c r="L23" s="17"/>
       <c r="M23" s="21" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N23" s="14">
         <v>1</v>
@@ -2383,7 +2382,7 @@
       </c>
       <c r="L24" s="17"/>
       <c r="M24" s="21" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="N24" s="14">
         <v>1</v>
@@ -2445,7 +2444,7 @@
       </c>
       <c r="L25" s="17"/>
       <c r="M25" s="21" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="N25" s="14">
         <v>1</v>
@@ -2507,7 +2506,7 @@
       </c>
       <c r="L26" s="26"/>
       <c r="M26" s="21" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="N26" s="14">
         <v>1</v>
@@ -2553,7 +2552,7 @@
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="21" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="N27" s="14">
         <v>1</v>
@@ -2562,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="19"/>
       <c r="R27" s="21"/>
@@ -2599,7 +2598,7 @@
       </c>
       <c r="L28" s="26"/>
       <c r="M28" s="21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N28" s="14">
         <v>1</v>
@@ -2645,7 +2644,7 @@
       </c>
       <c r="L29" s="26"/>
       <c r="M29" s="21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N29" s="14">
         <v>1</v>
@@ -2691,7 +2690,7 @@
       </c>
       <c r="L30" s="26"/>
       <c r="M30" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N30" s="14">
         <v>1</v>
@@ -2737,7 +2736,7 @@
       </c>
       <c r="L31" s="26"/>
       <c r="M31" s="21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N31" s="14">
         <v>1</v>
@@ -2783,7 +2782,7 @@
       </c>
       <c r="L32" s="26"/>
       <c r="M32" s="21" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="N32" s="14">
         <v>1</v>
@@ -2829,7 +2828,7 @@
       </c>
       <c r="L33" s="26"/>
       <c r="M33" s="21" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="N33" s="14">
         <v>1</v>
@@ -2875,7 +2874,7 @@
       </c>
       <c r="L34" s="26"/>
       <c r="M34" s="21" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="N34" s="14">
         <v>1</v>
@@ -2921,7 +2920,7 @@
       </c>
       <c r="L35" s="26"/>
       <c r="M35" s="21" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="N35" s="14">
         <v>1</v>
@@ -2967,7 +2966,7 @@
       </c>
       <c r="L36" s="26"/>
       <c r="M36" s="21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N36" s="14">
         <v>1</v>
@@ -3013,7 +3012,7 @@
       </c>
       <c r="L37" s="26"/>
       <c r="M37" s="21" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="N37" s="14">
         <v>1</v>
@@ -3059,7 +3058,7 @@
       </c>
       <c r="L38" s="26"/>
       <c r="M38" s="21" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N38" s="14">
         <v>1</v>
@@ -3105,7 +3104,7 @@
       </c>
       <c r="L39" s="26"/>
       <c r="M39" s="21" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="N39" s="14">
         <v>1</v>
@@ -3151,7 +3150,7 @@
       </c>
       <c r="L40" s="26"/>
       <c r="M40" s="21" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="N40" s="14">
         <v>1</v>
@@ -3197,7 +3196,7 @@
       </c>
       <c r="L41" s="26"/>
       <c r="M41" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N41" s="14">
         <v>1</v>
@@ -3243,7 +3242,7 @@
       </c>
       <c r="L42" s="26"/>
       <c r="M42" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N42" s="14">
         <v>1</v>
@@ -3289,7 +3288,7 @@
       </c>
       <c r="L43" s="26"/>
       <c r="M43" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N43" s="14">
         <v>1</v>
@@ -3335,7 +3334,7 @@
       </c>
       <c r="L44" s="26"/>
       <c r="M44" s="21" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="N44" s="14">
         <v>1</v>
@@ -3381,13 +3380,13 @@
       </c>
       <c r="L45" s="26"/>
       <c r="M45" s="21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" s="14">
         <v>1</v>
       </c>
       <c r="O45" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="16">
         <v>0</v>
@@ -3426,10 +3425,18 @@
         <v>0</v>
       </c>
       <c r="L46" s="26"/>
-      <c r="M46" s="21"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
+      <c r="M46" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="14">
+        <v>1</v>
+      </c>
+      <c r="O46" s="15">
+        <v>0</v>
+      </c>
+      <c r="P46" s="16">
+        <v>0</v>
+      </c>
       <c r="Q46" s="23"/>
       <c r="R46" s="1"/>
       <c r="S46" s="25"/>
@@ -3785,7 +3792,7 @@
     </row>
     <row r="56" spans="1:26" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
@@ -3821,7 +3828,45 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:26" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="24">
+        <v>55</v>
+      </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I57" s="14">
+        <v>1</v>
+      </c>
+      <c r="J57" s="15">
+        <v>0</v>
+      </c>
+      <c r="K57" s="16">
+        <v>0</v>
+      </c>
+      <c r="L57" s="27"/>
+      <c r="M57" s="27"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="27"/>
+      <c r="R57" s="27"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="27"/>
+      <c r="W57" s="27"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+    </row>
+    <row r="58" spans="1:26" ht="14.25" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M3:P45">
     <sortCondition descending="1" ref="N3:N45"/>
